--- a/stories/arbres/ATOM-REL.PAR.002-07.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.002-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gwenaëlle est dans la chambre avec maman. Il y a une cuisine en bois. Hervé joue déjà au robinet. L'eau factice coule. Gwenaëlle a envie. Elle s'approche. Maman dit : on peut attendre. Attendre, c'est rester près. Gwenaëlle pose les pieds au sol. Elle compte. Un. Deux. Trois. Hervé joue encore. Gwenaëlle attend. Maman tient sa main. Le bois est lisse. Hervé s'écarte. Maman dit : puis mon tour. Gwenaëlle dit : puis mon tour. Elle tourne le robinet. Ses mains sont calmes. Hervé attend maintenant. Papa passe la tête. Il dit : on attend. Puis mon tour arrive. Gwenaëlle sourit.</t>
+          <t>Gwenaëlle est dans la chambre avec maman. Il y a une cuisine en bois. Hervé joue déjà au robinet. L'eau factice coule. Gwenaëlle a envie. Elle s'approche. On peut attendre. Attendre, c'est rester près. Gwenaëlle pose les pieds au sol. Elle compte. Un. Deux. Trois. Hervé joue encore. Gwenaëlle attend. Maman tient sa main. Le bois est lisse. Hervé s'écarte. Puis mon tour. Puis mon tour. Elle tourne le robinet. Ses mains sont calmes. Hervé attend maintenant. Papa passe la tête. On attend. Puis mon tour arrive. Gwenaëlle sourit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Gwenaëlle est dans la chambre avec maman. Il y a une cuisine en bois. Hervé joue déjà au robinet. L'eau factice coule. Gwenaëlle a envie. Elle s'approche.
+maman|On peut attendre. Attendre, c'est rester près.
+narrateur|Gwenaëlle pose les pieds au sol. Elle compte. Un. Deux. Trois. Hervé joue encore. Gwenaëlle attend. Maman tient sa main. Le bois est lisse. Hervé s'écarte.
+maman|Puis mon tour.
+enfant-f|Puis mon tour. Elle tourne le robinet. Ses mains sont calmes.
+narrateur|Hervé attend maintenant. Papa passe la tête.
+narrateur|On attend.
+narrateur|Puis mon tour arrive. Gwenaëlle sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Hervé joue au robinet. Que fait Gwenaëlle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1666,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Gwenaëlle a su attendre. Puis mon tour est venu. Elle a tourné le robinet. Maman est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1833,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Gwenaëlle range la casserole. Elle prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2000,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2040,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.PAR.002-07.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.002-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,7 @@
 narrateur|Puis mon tour arrive. Gwenaëlle sourit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1506,7 @@
           <t>narrateur|Hervé joue au robinet. Que fait Gwenaëlle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1678,7 @@
           <t>narrateur|Gwenaëlle a su attendre. Puis mon tour est venu. Elle a tourné le robinet. Maman est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1838,6 +1846,7 @@
           <t>narrateur|Gwenaëlle range la casserole. Elle prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2005,6 +2014,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2023,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2047,6 +2057,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2272,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.PAR.002-07.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.002-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gwenaëlle attend le robinet en bois</t>
+          <t>Victorina attend le robinet</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>REL.PAR.001</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une cuillère en bois dort sous le rideau. Victorino joue au robinet. Victorina attend, la casserole sur les genoux. Puis c'est son tour.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gwenaëlle est dans la chambre avec maman. Il y a une cuisine en bois. Hervé joue déjà au robinet. L'eau factice coule. Gwenaëlle a envie. Elle s'approche. On peut attendre. Attendre, c'est rester près. Gwenaëlle pose les pieds au sol. Elle compte. Un. Deux. Trois. Hervé joue encore. Gwenaëlle attend. Maman tient sa main. Le bois est lisse. Hervé s'écarte. Puis mon tour. Puis mon tour. Elle tourne le robinet. Ses mains sont calmes. Hervé attend maintenant. Papa passe la tête. On attend. Puis mon tour arrive. Gwenaëlle sourit.</t>
+          <t>Une cuillère en bois dort sous le rideau. Le rideau bouge un peu, tout doux. Un rayon entre dans la chambre. Il pose sur la petite cuisine en bois. Ça sent le bois, un peu le citron. Victorina habite ici, avec maman et papa. Les tasses en bois sont alignées. Une casserole rouge attend par terre. Tu as vu la cuillère, Victorina ? Elle dormait, maman. On la pose près des tasses ? Victorina pose la cuillère. Le bois est lisse sous ses doigts. En ce moment, Victorino est déjà là. Il joue au robinet en bois. L'eau factice coule, tout doux. Le robinet fait un petit clic. Victorina a envie du robinet. Maman, je veux le robinet. On peut attendre. Victorino finit son tour. Puis c'est le tien. Victorina pose les pieds au sol. Elle met la casserole sur ses genoux. Elle reste près de maman. Victorino tourne encore le robinet. Tu attends bien, Victorina. Tes pieds restent au sol. Bravo. Papa pousse un peu la porte. Vous jouez à la cuisine ? Oui, papa. Tu attends ton tour ? Oui. Bravo. C'est du bon travail. Le bois du robinet est lisse. Victorina attend. On reste près. Puis ce sera ton tour. Victorino s'écarte un peu. Victorina serre la casserole.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1329,48 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Gwenaëlle est dans la chambre avec maman. Il y a une cuisine en bois. Hervé joue déjà au robinet. L'eau factice coule. Gwenaëlle a envie. Elle s'approche.
-maman|On peut attendre. Attendre, c'est rester près.
-narrateur|Gwenaëlle pose les pieds au sol. Elle compte. Un. Deux. Trois. Hervé joue encore. Gwenaëlle attend. Maman tient sa main. Le bois est lisse. Hervé s'écarte.
-maman|Puis mon tour.
-enfant-f|Puis mon tour. Elle tourne le robinet. Ses mains sont calmes.
-narrateur|Hervé attend maintenant. Papa passe la tête.
-narrateur|On attend.
-narrateur|Puis mon tour arrive. Gwenaëlle sourit.</t>
+          <t>narrateur|Une cuillère en bois dort sous le rideau.
+narrateur|Le rideau bouge un peu, tout doux.
+narrateur|Un rayon entre dans la chambre.
+narrateur|Il pose sur la petite cuisine en bois.
+narrateur|Ça sent le bois, un peu le citron.
+narrateur|Victorina habite ici, avec maman et papa.
+narrateur|Les tasses en bois sont alignées.
+narrateur|Une casserole rouge attend par terre.
+maman|Tu as vu la cuillère, Victorina ?
+enfant-f|Elle dormait, maman.
+maman|On la pose près des tasses ?
+narrateur|Victorina pose la cuillère.
+narrateur|Le bois est lisse sous ses doigts.
+narrateur|En ce moment, Victorino est déjà là.
+narrateur|Il joue au robinet en bois.
+narrateur|L'eau factice coule, tout doux.
+narrateur|Le robinet fait un petit clic.
+narrateur|Victorina a envie du robinet.
+enfant-f|Maman, je veux le robinet.
+maman|On peut attendre.
+maman|Victorino finit son tour.
+maman|Puis c'est le tien.
+narrateur|Victorina pose les pieds au sol.
+narrateur|Elle met la casserole sur ses genoux.
+narrateur|Elle reste près de maman.
+narrateur|Victorino tourne encore le robinet.
+maman|Tu attends bien, Victorina.
+maman|Tes pieds restent au sol.
+maman|Bravo.
+narrateur|Papa pousse un peu la porte.
+papa|Vous jouez à la cuisine ?
+enfant-f|Oui, papa.
+papa|Tu attends ton tour ?
+enfant-f|Oui.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Le bois du robinet est lisse.
+narrateur|Victorina attend.
+maman|On reste près.
+maman|Puis ce sera ton tour.
+narrateur|Victorino s'écarte un peu.
+narrateur|Victorina serre la casserole.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1347,7 +1398,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Hervé joue au robinet. Que fait Gwenaëlle ?</t>
+          <t>Victorino joue au robinet. Que fait Victorina ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1503,7 +1554,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Hervé joue au robinet. Que fait Gwenaëlle ?</t>
+          <t>narrateur|Victorino joue au robinet.
+narrateur|Que fait Victorina ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1531,7 +1583,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Gwenaëlle a su attendre. Puis mon tour est venu. Elle a tourné le robinet. Maman est là.</t>
+          <t>Victorino laisse le robinet. Maintenant. Puis c'est ton tour. Puis mon tour. Victorina pose la casserole. Elle tourne le robinet. Ses mains sont calmes. L'eau factice coule encore. Bravo, Victorina. Tu as attendu. C'est du bon travail. Tu as bien attendu, ma puce. Le bois est lisse, papa. Oui. Il est doux. Victorino attend maintenant, près des tasses. Parce que tu as attendu, c'est ton tour. La casserole reçoit un peu d'eau factice.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1675,7 +1727,24 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Gwenaëlle a su attendre. Puis mon tour est venu. Elle a tourné le robinet. Maman est là.</t>
+          <t>narrateur|Victorino laisse le robinet.
+maman|Maintenant.
+maman|Puis c'est ton tour.
+enfant-f|Puis mon tour.
+narrateur|Victorina pose la casserole.
+narrateur|Elle tourne le robinet.
+narrateur|Ses mains sont calmes.
+narrateur|L'eau factice coule encore.
+maman|Bravo, Victorina.
+maman|Tu as attendu.
+maman|C'est du bon travail.
+papa|Tu as bien attendu, ma puce.
+enfant-f|Le bois est lisse, papa.
+papa|Oui.
+papa|Il est doux.
+narrateur|Victorino attend maintenant, près des tasses.
+maman|Parce que tu as attendu, c'est ton tour.
+narrateur|La casserole reçoit un peu d'eau factice.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1703,7 +1772,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Gwenaëlle range la casserole. Elle prend la main de maman.</t>
+          <t>Victorina range la casserole. Tu veux laisser le robinet à Victorino ? Oui, maman. Bravo. On peut prêter. Victorino reprend le robinet. Victorina prend la main de maman. On range les tasses, aussi ? Oui, papa. Les tasses reviennent en rang. Tu as fini de ranger tes tasses ? Oui, maman. Bravo. Tu as bien attendu, Victorina. Puis c'était mon tour. Oui. Puis ton tour. Le rideau bouge encore un peu. La petite cuisine est calme.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1843,7 +1912,25 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Gwenaëlle range la casserole. Elle prend la main de maman.</t>
+          <t>narrateur|Victorina range la casserole.
+maman|Tu veux laisser le robinet à Victorino ?
+enfant-f|Oui, maman.
+maman|Bravo.
+maman|On peut prêter.
+narrateur|Victorino reprend le robinet.
+narrateur|Victorina prend la main de maman.
+papa|On range les tasses, aussi ?
+enfant-f|Oui, papa.
+narrateur|Les tasses reviennent en rang.
+maman|Tu as fini de ranger tes tasses ?
+enfant-f|Oui, maman.
+maman|Bravo.
+papa|Tu as bien attendu, Victorina.
+enfant-f|Puis c'était mon tour.
+papa|Oui.
+papa|Puis ton tour.
+narrateur|Le rideau bouge encore un peu.
+maman|La petite cuisine est calme.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1871,7 +1958,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai tourné le robinet. Bravo, Victorina. Tu as fait du bon travail. La cuillère en bois reste près des tasses. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2011,7 +2098,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai attendu.
+enfant-f|Puis j'ai tourné le robinet.
+maman|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+narrateur|La cuillère en bois reste près des tasses.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2033,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2071,6 +2163,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.PAR.002-07.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.002-07.xlsx
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une cuillère en bois dort sous le rideau. Le rideau bouge un peu, tout doux. Un rayon entre dans la chambre. Il pose sur la petite cuisine en bois. Ça sent le bois, un peu le citron. Victorina habite ici, avec maman et papa. Les tasses en bois sont alignées. Une casserole rouge attend par terre. Tu as vu la cuillère, Victorina ? Elle dormait, maman. On la pose près des tasses ? Victorina pose la cuillère. Le bois est lisse sous ses doigts. En ce moment, Victorino est déjà là. Il joue au robinet en bois. L'eau factice coule, tout doux. Le robinet fait un petit clic. Victorina a envie du robinet. Maman, je veux le robinet. On peut attendre. Victorino finit son tour. Puis c'est le tien. Victorina pose les pieds au sol. Elle met la casserole sur ses genoux. Elle reste près de maman. Victorino tourne encore le robinet. Tu attends bien, Victorina. Tes pieds restent au sol. Bravo. Papa pousse un peu la porte. Vous jouez à la cuisine ? Oui, papa. Tu attends ton tour ? Oui. Bravo. C'est du bon travail. Le bois du robinet est lisse. Victorina attend. On reste près. Puis ce sera ton tour. Victorino s'écarte un peu. Victorina serre la casserole.</t>
+          <t>Une cuillère en bois dort sous le rideau. Le rideau bouge un peu, tout doux. Un rayon entre dans la chambre. Il pose sur la petite cuisine en bois. Ça sent le bois, un peu le citron. Victorina habite ici, avec maman et papa. Les tasses en bois sont alignées. Une casserole rouge attend par terre. Tu as vu la cuillère, Victorina ? Elle dormait, maman. On la pose près des tasses ? Victorina pose la cuillère. Le bois est lisse sous ses doigts. En ce moment, Victorino est déjà là. Il joue au robinet en bois. L'eau factice coule, tout doux. Le robinet fait un petit clic. Victorina a envie du robinet. Maman, je veux le robinet. On peut attendre. Victorino finit son tour. Puis c'est le tien. Victorina pose les pieds au sol. Elle met la casserole sur ses genoux. Elle reste près de maman. Victorino tourne encore le robinet. Tu attends bien, Victorina. Tes pieds restent au sol. Bravo. Papa pousse un peu la porte. Vous jouez à la cuisine ? Oui, papa. Tu attends ton tour ? Oui. Bravo. Le bois du robinet est lisse. Victorina attend. On reste près. Puis ce sera ton tour. Victorino s'écarte un peu. Victorina serre la casserole.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gwenaëlle est dans la chambre avec maman. Il y a une cuisine en bois. Hervé joue déjà au robinet. L'eau factice coule. Gwenaëlle a envie. Elle s'approche. Maman dit : on peut &lt;emphasis level="moderate"&gt;attendre&lt;/emphasis&gt;. Attendre, c'est rester près. Gwenaëlle pose les pieds au sol. Elle compte. Un. Deux. Trois. Hervé joue encore. Gwenaëlle attend. Maman tient sa main. Le bois est lisse. Hervé s'écarte. Maman dit : puis mon tour. Gwenaëlle dit : puis mon tour. Elle tourne le robinet. Ses mains sont calmes. Hervé attend maintenant. Papa passe la tête. Il dit : on attend. Puis mon tour arrive. Gwenaëlle sourit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une cuillère en bois dort sous le rideau. Le rideau bouge un peu, tout doux. Un rayon entre dans la chambre. Il pose sur la petite cuisine en bois. Ça sent le bois, un peu le citron. Victorina habite ici, avec maman et papa. Les tasses en bois sont alignées. Une casserole rouge attend par terre. Tu as vu la cuillère, Victorina ? Elle dormait, maman. On la pose près des tasses ? Victorina pose la cuillère. Le bois est lisse sous ses doigts. En ce moment, Victorino est déjà là. Il joue au robinet en bois. L'eau factice coule, tout doux. Le robinet fait un petit clic. Victorina a envie du robinet. Maman, je veux le robinet. On peut attendre. Victorino finit son tour. Puis c'est le tien. Victorina pose les pieds au sol. Elle met la casserole sur ses genoux. Elle reste près de maman. Victorino tourne encore le robinet. Tu attends bien, Victorina. Tes pieds restent au sol. Bravo. Papa pousse un peu la porte. Vous jouez à la cuisine ? Oui, papa. Tu attends ton tour ? Oui. Bravo. Le bois du robinet est lisse. Victorina attend. On reste près. Puis ce sera ton tour. Victorino s'écarte un peu. Victorina serre la casserole.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1364,7 +1364,6 @@
 papa|Tu attends ton tour ?
 enfant-f|Oui.
 papa|Bravo.
-papa|C'est du bon travail.
 narrateur|Le bois du robinet est lisse.
 narrateur|Victorina attend.
 maman|On reste près.
@@ -1373,7 +1372,6 @@
 narrateur|Victorina serre la casserole.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1403,7 +1401,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hervé joue au robinet. Que fait Gwenaëlle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino joue au robinet. Que fait Victorina ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1558,7 +1556,6 @@
 narrateur|Que fait Victorina ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1583,12 +1580,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorino laisse le robinet. Maintenant. Puis c'est ton tour. Puis mon tour. Victorina pose la casserole. Elle tourne le robinet. Ses mains sont calmes. L'eau factice coule encore. Bravo, Victorina. Tu as attendu. C'est du bon travail. Tu as bien attendu, ma puce. Le bois est lisse, papa. Oui. Il est doux. Victorino attend maintenant, près des tasses. Parce que tu as attendu, c'est ton tour. La casserole reçoit un peu d'eau factice.</t>
+          <t>Victorino laisse le robinet. Maintenant. Puis c'est ton tour. Puis mon tour. Victorina pose la casserole. Elle tourne le robinet. Ses mains sont calmes. L'eau factice coule encore. Bravo, Victorina. Tu as attendu. Tu as bien attendu, ma puce. Le bois est lisse, papa. Oui. Il est doux. Victorino attend maintenant, près des tasses. Parce que tu as attendu, c'est ton tour. La casserole reçoit un peu d'eau factice.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gwenaëlle a su &lt;emphasis level="moderate"&gt;attendre&lt;/emphasis&gt;. Puis mon tour est venu. Elle a tourné le robinet. Maman est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino laisse le robinet. Maintenant. Puis c'est ton tour. Puis mon tour. Victorina pose la casserole. Elle tourne le robinet. Ses mains sont calmes. L'eau factice coule encore. Bravo, Victorina. Tu as attendu. Tu as bien attendu, ma puce. Le bois est lisse, papa. Oui. Il est doux. Victorino attend maintenant, près des tasses. Parce que tu as attendu, c'est ton tour. La casserole reçoit un peu d'eau factice.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1737,7 +1734,6 @@
 narrateur|L'eau factice coule encore.
 maman|Bravo, Victorina.
 maman|Tu as attendu.
-maman|C'est du bon travail.
 papa|Tu as bien attendu, ma puce.
 enfant-f|Le bois est lisse, papa.
 papa|Oui.
@@ -1747,7 +1743,6 @@
 narrateur|La casserole reçoit un peu d'eau factice.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1777,7 +1772,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gwenaëlle range la casserole. Elle prend la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina range la casserole. Tu veux laisser le robinet à Victorino ? Oui, maman. Bravo. On peut prêter. Victorino reprend le robinet. Victorina prend la main de maman. On range les tasses, aussi ? Oui, papa. Les tasses reviennent en rang. Tu as fini de ranger tes tasses ? Oui, maman. Bravo. Tu as bien attendu, Victorina. Puis c'était mon tour. Oui. Puis ton tour. Le rideau bouge encore un peu. La petite cuisine est calme.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1933,7 +1928,6 @@
 maman|La petite cuisine est calme.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1958,12 +1952,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai attendu. Puis j'ai tourné le robinet. Bravo, Victorina. Tu as fait du bon travail. La cuillère en bois reste près des tasses. L'histoire est finie.</t>
+          <t>J'ai attendu. Puis j'ai tourné le robinet. Bravo, Victorina. La cuillère en bois reste près des tasses.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai attendu. Puis j'ai tourné le robinet. Bravo, Victorina. La cuillère en bois reste près des tasses.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2101,12 +2095,9 @@
           <t>enfant-f|J'ai attendu.
 enfant-f|Puis j'ai tourné le robinet.
 maman|Bravo, Victorina.
-papa|Tu as fait du bon travail.
-narrateur|La cuillère en bois reste près des tasses.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La cuillère en bois reste près des tasses.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2125,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2170,6 +2161,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.PAR.002-07.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.002-07.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gwenaëlle, Hervé, maman, papa</t>
+          <t>Victorina, Victorino, maman, papa</t>
         </is>
       </c>
     </row>
